--- a/баги.xlsx
+++ b/баги.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Вано\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Z:\3-МД-5 ПИ\Бурчевский и\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AA21A6E4-8C32-417F-B290-B3A6B02B0817}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD1DE8E7-D493-4A8B-BEAF-B4C7EA896CC1}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="24210" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="96">
   <si>
     <t>Номер кейса</t>
   </si>
@@ -284,6 +284,48 @@
   </si>
   <si>
     <t>Серьезность</t>
+  </si>
+  <si>
+    <t>1)Добавить модификатор "Ocean"  
+2)В настройке модификатора "wawes" увеличить параметр "scale"</t>
+  </si>
+  <si>
+    <t>Взаимодействие персонажа с водой</t>
+  </si>
+  <si>
+    <t>1)Подойти к любому водоему 
+2) направить персонажа в сам водоем</t>
+  </si>
+  <si>
+    <t>Взаимодействие тела персонажа с внутриигровыми объектами</t>
+  </si>
+  <si>
+    <t>1)Подойти к сущности "великан"
+2) начать с ним бой,
+ 3)умереть от его атаки дубиной</t>
+  </si>
+  <si>
+    <t>Проверка поведения неигровых враждебных сущностей</t>
+  </si>
+  <si>
+    <t>Кабан имеет паузу между атаками, позволяющую игроку среагировать на атаку</t>
+  </si>
+  <si>
+    <t>Проверка взаимодействия физики авто с динамическими объектами</t>
+  </si>
+  <si>
+    <t>1)Сесть в любое транспортное средство
+2)Подъехать к объекту, расположенному в ряде локаций
+3)Инициировать взаимодействие коллайдеров автомобиля и динамического объекта</t>
+  </si>
+  <si>
+    <t>Реализация возврата на предыдущую страницу</t>
+  </si>
+  <si>
+    <t>Проверка отображения корректных данных о концертах на основе геоданных</t>
+  </si>
+  <si>
+    <t>Проверка единообразности оформления различных страниц приложения</t>
   </si>
 </sst>
 </file>
@@ -617,7 +659,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I8"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.85546875" style="1" customWidth="1"/>
@@ -661,7 +703,7 @@
       </c>
     </row>
     <row r="2" spans="1:9" ht="120" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
+      <c r="A2" s="4">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -732,7 +774,7 @@
         <v>30</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>31</v>
+        <v>84</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>32</v>
@@ -747,21 +789,208 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H5" s="2"/>
-      <c r="I5" s="1"/>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H6" s="2"/>
-      <c r="I6" s="1"/>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H7" s="2"/>
-      <c r="I7" s="1"/>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="H8" s="2"/>
-      <c r="I8" s="1"/>
+    <row r="5" spans="1:9" ht="195" x14ac:dyDescent="0.25">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>18</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
